--- a/FotosMedidas/Medidas.xlsx
+++ b/FotosMedidas/Medidas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andry\OneDrive - Megabazar SpA\Documentos\GitHub\FotosMH\FotosMedidas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://megabazarspa-my.sharepoint.com/personal/contacto_yassne_com/Documents/Documentos/GitHub/FotosMH/FotosMedidas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287E78B4-B7D8-4D36-956E-B3587161E77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{287E78B4-B7D8-4D36-956E-B3587161E77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F32D8933-FD10-4526-B34C-C0BFF7217D4A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
@@ -587,7 +587,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8072300C-2004-442D-A692-809CCCFA06E4}">
   <dimension ref="B2:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
@@ -606,66 +606,66 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
-        <v>25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
